--- a/Rescource/Stage3.xlsx
+++ b/Rescource/Stage3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\MapData\Rescource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B52018-5D56-485B-9420-AF19080A74F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C469EC50-EE0C-4739-BC1D-B1F63D94E886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="165" windowWidth="21000" windowHeight="14880" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
+    <workbookView xWindow="570" yWindow="-16005" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,25 +131,25 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>54</xdr:col>
-          <xdr:colOff>104775</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>123825</xdr:rowOff>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>228600</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>63</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>142875</xdr:rowOff>
+          <xdr:col>60</xdr:col>
+          <xdr:colOff>47625</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1025" name="Button 1" hidden="1">
+            <xdr:cNvPr id="1026" name="Button 2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1025"/>
+                  <a14:compatExt spid="_x0000_s1026"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -185,7 +185,7 @@
                   <a:latin typeface="游ゴシック"/>
                   <a:ea typeface="游ゴシック"/>
                 </a:rPr>
-                <a:t>ボタン 1</a:t>
+                <a:t>ボタン 2</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -2153,19 +2153,19 @@
         <v>1</v>
       </c>
       <c r="IB23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IC23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="ID23">
         <v>1</v>
       </c>
       <c r="IE23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IF23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IG23">
         <v>1</v>
@@ -2242,10 +2242,10 @@
         <v>1</v>
       </c>
       <c r="IR24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IS24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IT24">
         <v>1</v>
@@ -2319,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="JD25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JE25">
         <v>2</v>
@@ -2575,13 +2575,13 @@
         <v>1</v>
       </c>
       <c r="IK27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IL27">
         <v>2</v>
       </c>
       <c r="IM27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IN27">
         <v>1</v>
@@ -3271,6 +3271,9 @@
       </c>
       <c r="CH31">
         <v>1</v>
+      </c>
+      <c r="CS31">
+        <v>2</v>
       </c>
       <c r="DA31">
         <v>1</v>
@@ -4515,20 +4518,20 @@
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId4" name="Button 1">
+            <control shapeId="1026" r:id="rId4" name="Button 2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!Sheet1.ExportMap">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>54</xdr:col>
-                    <xdr:colOff>104775</xdr:colOff>
-                    <xdr:row>3</xdr:row>
-                    <xdr:rowOff>123825</xdr:rowOff>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>228600</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>63</xdr:col>
-                    <xdr:colOff>171450</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>142875</xdr:rowOff>
+                    <xdr:col>60</xdr:col>
+                    <xdr:colOff>47625</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>85725</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>

--- a/Rescource/Stage3.xlsx
+++ b/Rescource/Stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C469EC50-EE0C-4739-BC1D-B1F63D94E886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08C9E49-CCD7-41D7-944F-BD8339155020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="-16005" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -53,6 +53,13 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -85,7 +92,217 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="33">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -171,7 +388,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="22860" rIns="18288" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="41148" rIns="27432" bIns="41148" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -724,6 +941,9 @@
       <c r="EY5">
         <v>1</v>
       </c>
+      <c r="FC5">
+        <v>3</v>
+      </c>
       <c r="FR5">
         <v>1</v>
       </c>
@@ -903,6 +1123,9 @@
       <c r="F9">
         <v>1</v>
       </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
       <c r="Q9">
         <v>1</v>
       </c>
@@ -918,8 +1141,14 @@
       <c r="U9">
         <v>1</v>
       </c>
+      <c r="Z9">
+        <v>4</v>
+      </c>
       <c r="AD9">
         <v>1</v>
+      </c>
+      <c r="AH9">
+        <v>4</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -1194,6 +1423,9 @@
       <c r="EY12">
         <v>1</v>
       </c>
+      <c r="FD12">
+        <v>4</v>
+      </c>
       <c r="FI12">
         <v>1</v>
       </c>
@@ -1288,6 +1520,9 @@
       <c r="AW14">
         <v>1</v>
       </c>
+      <c r="CW14">
+        <v>5</v>
+      </c>
       <c r="EX14">
         <v>1</v>
       </c>
@@ -1385,6 +1620,9 @@
       <c r="K16">
         <v>1</v>
       </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
       <c r="Y16">
         <v>1</v>
       </c>
@@ -1399,6 +1637,9 @@
       </c>
       <c r="AC16">
         <v>1</v>
+      </c>
+      <c r="AG16">
+        <v>3</v>
       </c>
       <c r="AK16">
         <v>1</v>
@@ -1914,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="CN19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO19">
         <v>2</v>
@@ -1923,7 +2164,7 @@
         <v>2</v>
       </c>
       <c r="CQ19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CR19">
         <v>1</v>
@@ -2078,6 +2319,12 @@
       <c r="K22">
         <v>1</v>
       </c>
+      <c r="CH22">
+        <v>4</v>
+      </c>
+      <c r="CW22">
+        <v>3</v>
+      </c>
       <c r="EX22">
         <v>1</v>
       </c>
@@ -2092,6 +2339,9 @@
       </c>
       <c r="FR22">
         <v>1</v>
+      </c>
+      <c r="ID22">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:277" x14ac:dyDescent="0.4">
@@ -2146,6 +2396,9 @@
       <c r="FJ23">
         <v>1</v>
       </c>
+      <c r="FP23">
+        <v>3</v>
+      </c>
       <c r="FR23">
         <v>1</v>
       </c>
@@ -2169,6 +2422,9 @@
       </c>
       <c r="IG23">
         <v>1</v>
+      </c>
+      <c r="IT23">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:277" x14ac:dyDescent="0.4">
@@ -2256,6 +2512,9 @@
       <c r="IV24">
         <v>1</v>
       </c>
+      <c r="JN24">
+        <v>9</v>
+      </c>
     </row>
     <row r="25" spans="1:277" x14ac:dyDescent="0.4">
       <c r="A25">
@@ -2288,6 +2547,9 @@
       <c r="GJ25">
         <v>2</v>
       </c>
+      <c r="GY25">
+        <v>6</v>
+      </c>
       <c r="HU25">
         <v>1</v>
       </c>
@@ -2334,16 +2596,16 @@
         <v>1</v>
       </c>
       <c r="JI25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JJ25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JK25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JL25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="JM25">
         <v>1</v>
@@ -2500,10 +2762,10 @@
         <v>1</v>
       </c>
       <c r="CJ27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CK27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CL27">
         <v>1</v>
@@ -2624,6 +2886,9 @@
       <c r="A28">
         <v>1</v>
       </c>
+      <c r="Q28">
+        <v>4</v>
+      </c>
       <c r="CC28">
         <v>1</v>
       </c>
@@ -2716,6 +2981,12 @@
       </c>
       <c r="FJ28">
         <v>1</v>
+      </c>
+      <c r="FQ28">
+        <v>4</v>
+      </c>
+      <c r="FW28">
+        <v>4</v>
       </c>
       <c r="GR28">
         <v>1</v>
@@ -2935,11 +3206,17 @@
       <c r="GE29">
         <v>1</v>
       </c>
+      <c r="GM29">
+        <v>3</v>
+      </c>
       <c r="GR29">
         <v>1</v>
       </c>
       <c r="GS29">
         <v>1</v>
+      </c>
+      <c r="HG29">
+        <v>6</v>
       </c>
       <c r="HU29">
         <v>1</v>
@@ -2988,6 +3265,9 @@
       <c r="AE30">
         <v>1</v>
       </c>
+      <c r="BG30">
+        <v>3</v>
+      </c>
       <c r="BP30">
         <v>1</v>
       </c>
@@ -3305,6 +3585,15 @@
       <c r="EB31">
         <v>1</v>
       </c>
+      <c r="EG31">
+        <v>3</v>
+      </c>
+      <c r="EL31">
+        <v>4</v>
+      </c>
+      <c r="ER31">
+        <v>3</v>
+      </c>
       <c r="EW31">
         <v>2</v>
       </c>
@@ -3459,6 +3748,9 @@
       </c>
       <c r="AG32">
         <v>1</v>
+      </c>
+      <c r="AX32">
+        <v>3</v>
       </c>
       <c r="BC32">
         <v>1</v>
@@ -4497,16 +4789,31 @@
   </sortState>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A45:XFD1048576 A42:A44 AI42:XFD44 A1:XFD4 A5:A7 AJ5:XFD7 A8:XFD12 A24:XFD41 FA13:XFD23 A13:EY23">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="2">
+    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="2">
       <formula>NOT(ISERROR(SEARCH("2",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="1">
+    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="1">
       <formula>NOT(ISERROR(SEARCH("1",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="1">
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="1">
       <formula>NOT(ISERROR(SEARCH("1",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="3">
+      <formula>NOT(ISERROR(SEARCH("3",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="4">
+      <formula>NOT(ISERROR(SEARCH("4",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="5">
+      <formula>NOT(ISERROR(SEARCH("5",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="6">
+      <formula>NOT(ISERROR(SEARCH("6",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="9">
+      <formula>NOT(ISERROR(SEARCH("9",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Rescource/Stage3.xlsx
+++ b/Rescource/Stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08C9E49-CCD7-41D7-944F-BD8339155020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EECEA5F-CA14-43F8-AE0B-8E1B2461C622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
+    <workbookView xWindow="45" yWindow="-14340" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,42 +92,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -160,146 +125,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4789,30 +4614,30 @@
   </sortState>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A45:XFD1048576 A42:A44 AI42:XFD44 A1:XFD4 A5:A7 AJ5:XFD7 A8:XFD12 A24:XFD41 FA13:XFD23 A13:EY23">
-    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="2">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="2">
       <formula>NOT(ISERROR(SEARCH("2",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="1">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="1">
       <formula>NOT(ISERROR(SEARCH("1",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="1">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="1">
       <formula>NOT(ISERROR(SEARCH("1",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="3">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="3">
       <formula>NOT(ISERROR(SEARCH("3",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="4">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="4">
       <formula>NOT(ISERROR(SEARCH("4",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="5">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="5">
       <formula>NOT(ISERROR(SEARCH("5",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="6">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="6">
       <formula>NOT(ISERROR(SEARCH("6",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="9">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="9">
       <formula>NOT(ISERROR(SEARCH("9",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Rescource/Stage3.xlsx
+++ b/Rescource/Stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EECEA5F-CA14-43F8-AE0B-8E1B2461C622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A426C5-2B7A-458C-A371-97C1336BE01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="-14340" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
+    <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2544,6 +2544,9 @@
       <c r="C27">
         <v>2</v>
       </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
       <c r="G27">
         <v>2</v>
       </c>
@@ -3377,7 +3380,7 @@
       <c r="CH31">
         <v>1</v>
       </c>
-      <c r="CS31">
+      <c r="CR31">
         <v>2</v>
       </c>
       <c r="DA31">

--- a/Rescource/Stage3.xlsx
+++ b/Rescource/Stage3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A426C5-2B7A-458C-A371-97C1336BE01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDEC622-EE02-493B-819C-DC69FD4E4357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
   </bookViews>

--- a/Rescource/Stage3.xlsx
+++ b/Rescource/Stage3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDEC622-EE02-493B-819C-DC69FD4E4357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558BC7E7-03C3-4077-8B30-8B54CDD8609A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
   </bookViews>
@@ -766,7 +766,10 @@
       <c r="EY5">
         <v>1</v>
       </c>
-      <c r="FC5">
+      <c r="FA5">
+        <v>3</v>
+      </c>
+      <c r="FF5">
         <v>3</v>
       </c>
       <c r="FR5">
@@ -948,9 +951,6 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="L9">
-        <v>3</v>
-      </c>
       <c r="Q9">
         <v>1</v>
       </c>
@@ -974,6 +974,9 @@
       </c>
       <c r="AH9">
         <v>4</v>
+      </c>
+      <c r="AM9">
+        <v>3</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -1248,8 +1251,14 @@
       <c r="EY12">
         <v>1</v>
       </c>
+      <c r="FA12">
+        <v>3</v>
+      </c>
       <c r="FD12">
         <v>4</v>
+      </c>
+      <c r="FF12">
+        <v>3</v>
       </c>
       <c r="FI12">
         <v>1</v>
@@ -1345,8 +1354,14 @@
       <c r="AW14">
         <v>1</v>
       </c>
+      <c r="CR14">
+        <v>3</v>
+      </c>
       <c r="CW14">
         <v>5</v>
+      </c>
+      <c r="CZ14">
+        <v>3</v>
       </c>
       <c r="EX14">
         <v>1</v>
@@ -1445,9 +1460,6 @@
       <c r="K16">
         <v>1</v>
       </c>
-      <c r="N16">
-        <v>3</v>
-      </c>
       <c r="Y16">
         <v>1</v>
       </c>
@@ -1462,9 +1474,6 @@
       </c>
       <c r="AC16">
         <v>1</v>
-      </c>
-      <c r="AG16">
-        <v>3</v>
       </c>
       <c r="AK16">
         <v>1</v>
@@ -2144,12 +2153,21 @@
       <c r="K22">
         <v>1</v>
       </c>
+      <c r="CD22">
+        <v>3</v>
+      </c>
       <c r="CH22">
         <v>4</v>
       </c>
-      <c r="CW22">
+      <c r="CJ22">
         <v>3</v>
       </c>
+      <c r="CT22">
+        <v>3</v>
+      </c>
+      <c r="CZ22">
+        <v>3</v>
+      </c>
       <c r="EX22">
         <v>1</v>
       </c>
@@ -2165,7 +2183,10 @@
       <c r="FR22">
         <v>1</v>
       </c>
-      <c r="ID22">
+      <c r="HZ22">
+        <v>3</v>
+      </c>
+      <c r="IH22">
         <v>3</v>
       </c>
     </row>
@@ -2204,7 +2225,7 @@
         <v>1</v>
       </c>
       <c r="CW23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CX23">
         <v>1</v>
@@ -2221,7 +2242,7 @@
       <c r="FJ23">
         <v>1</v>
       </c>
-      <c r="FP23">
+      <c r="FL23">
         <v>3</v>
       </c>
       <c r="FR23">
@@ -2247,9 +2268,15 @@
       </c>
       <c r="IG23">
         <v>1</v>
+      </c>
+      <c r="IP23">
+        <v>3</v>
       </c>
       <c r="IT23">
         <v>4</v>
+      </c>
+      <c r="IW23">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:277" x14ac:dyDescent="0.4">
@@ -2372,8 +2399,14 @@
       <c r="GJ25">
         <v>2</v>
       </c>
+      <c r="GV25">
+        <v>3</v>
+      </c>
       <c r="GY25">
         <v>6</v>
+      </c>
+      <c r="HA25">
+        <v>3</v>
       </c>
       <c r="HU25">
         <v>1</v>
@@ -2714,9 +2747,15 @@
       <c r="A28">
         <v>1</v>
       </c>
+      <c r="M28">
+        <v>3</v>
+      </c>
       <c r="Q28">
         <v>4</v>
       </c>
+      <c r="S28">
+        <v>3</v>
+      </c>
       <c r="CC28">
         <v>1</v>
       </c>
@@ -2815,6 +2854,9 @@
       </c>
       <c r="FW28">
         <v>4</v>
+      </c>
+      <c r="GB28">
+        <v>3</v>
       </c>
       <c r="GR28">
         <v>1</v>
@@ -3034,17 +3076,26 @@
       <c r="GE29">
         <v>1</v>
       </c>
-      <c r="GM29">
+      <c r="GK29">
         <v>3</v>
       </c>
+      <c r="GO29">
+        <v>3</v>
+      </c>
       <c r="GR29">
         <v>1</v>
       </c>
       <c r="GS29">
         <v>1</v>
+      </c>
+      <c r="HC29">
+        <v>3</v>
       </c>
       <c r="HG29">
         <v>6</v>
+      </c>
+      <c r="HK29">
+        <v>3</v>
       </c>
       <c r="HU29">
         <v>1</v>
@@ -3093,7 +3144,10 @@
       <c r="AE30">
         <v>1</v>
       </c>
-      <c r="BG30">
+      <c r="BB30">
+        <v>3</v>
+      </c>
+      <c r="BL30">
         <v>3</v>
       </c>
       <c r="BP30">
@@ -3413,14 +3467,8 @@
       <c r="EB31">
         <v>1</v>
       </c>
-      <c r="EG31">
-        <v>3</v>
-      </c>
       <c r="EL31">
         <v>4</v>
-      </c>
-      <c r="ER31">
-        <v>3</v>
       </c>
       <c r="EW31">
         <v>2</v>
@@ -3577,7 +3625,7 @@
       <c r="AG32">
         <v>1</v>
       </c>
-      <c r="AX32">
+      <c r="AL32">
         <v>3</v>
       </c>
       <c r="BC32">

--- a/Rescource/Stage3.xlsx
+++ b/Rescource/Stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558BC7E7-03C3-4077-8B30-8B54CDD8609A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A22C1D-6E40-4191-A745-29ED345B98C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
+    <workbookView xWindow="870" yWindow="675" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2494,6 +2494,18 @@
       <c r="K26">
         <v>1</v>
       </c>
+      <c r="BZ26">
+        <v>3</v>
+      </c>
+      <c r="CN26">
+        <v>3</v>
+      </c>
+      <c r="DJ26">
+        <v>3</v>
+      </c>
+      <c r="DS26">
+        <v>3</v>
+      </c>
       <c r="FI26">
         <v>1</v>
       </c>
@@ -2962,6 +2974,12 @@
       <c r="AX29">
         <v>2</v>
       </c>
+      <c r="BO29">
+        <v>3</v>
+      </c>
+      <c r="BX29">
+        <v>3</v>
+      </c>
       <c r="CD29">
         <v>1</v>
       </c>
@@ -2982,6 +3000,12 @@
       </c>
       <c r="CJ29">
         <v>1</v>
+      </c>
+      <c r="CY29">
+        <v>3</v>
+      </c>
+      <c r="DH29">
+        <v>3</v>
       </c>
       <c r="DM29">
         <v>1</v>

--- a/Rescource/Stage3.xlsx
+++ b/Rescource/Stage3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A22C1D-6E40-4191-A745-29ED345B98C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EB5D41-5453-498D-B681-D30CE28901A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="675" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
+    <workbookView xWindow="75" yWindow="-14820" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1408,19 +1408,19 @@
         <v>1</v>
       </c>
       <c r="CT15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CU15">
         <v>1</v>
       </c>
       <c r="CV15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CW15">
         <v>1</v>
       </c>
       <c r="CX15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CY15">
         <v>1</v>
@@ -2578,6 +2578,9 @@
       <c r="JP26">
         <v>1</v>
       </c>
+      <c r="JQ26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:277" x14ac:dyDescent="0.4">
       <c r="A27">
@@ -2754,6 +2757,12 @@
       <c r="JO27">
         <v>1</v>
       </c>
+      <c r="JP27">
+        <v>1</v>
+      </c>
+      <c r="JQ27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:277" x14ac:dyDescent="0.4">
       <c r="A28">
@@ -2930,6 +2939,15 @@
       <c r="JN28">
         <v>1</v>
       </c>
+      <c r="JO28">
+        <v>1</v>
+      </c>
+      <c r="JP28">
+        <v>1</v>
+      </c>
+      <c r="JQ28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:277" x14ac:dyDescent="0.4">
       <c r="A29">
@@ -3148,6 +3166,18 @@
       <c r="JM29">
         <v>1</v>
       </c>
+      <c r="JN29">
+        <v>1</v>
+      </c>
+      <c r="JO29">
+        <v>1</v>
+      </c>
+      <c r="JP29">
+        <v>1</v>
+      </c>
+      <c r="JQ29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:277" x14ac:dyDescent="0.4">
       <c r="A30">
@@ -3349,19 +3379,19 @@
         <v>1</v>
       </c>
       <c r="HE30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HF30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HG30">
         <v>1</v>
       </c>
       <c r="HH30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HI30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="HJ30">
         <v>1</v>

--- a/Rescource/Stage3.xlsx
+++ b/Rescource/Stage3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EB5D41-5453-498D-B681-D30CE28901A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710B5DC7-DEEA-4628-B5FB-B1766AA09E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="75" yWindow="-14820" windowWidth="26850" windowHeight="14655" xr2:uid="{DD2E9687-477B-49CD-9B5F-ECA9F7187C25}"/>
   </bookViews>
@@ -1833,6 +1833,12 @@
       <c r="AW18">
         <v>1</v>
       </c>
+      <c r="CL18">
+        <v>3</v>
+      </c>
+      <c r="CS18">
+        <v>3</v>
+      </c>
       <c r="EX18">
         <v>1</v>
       </c>
@@ -2533,11 +2539,23 @@
       <c r="GZ26">
         <v>1</v>
       </c>
+      <c r="HL26">
+        <v>3</v>
+      </c>
+      <c r="HS26">
+        <v>3</v>
+      </c>
       <c r="HU26">
         <v>1</v>
       </c>
       <c r="HV26">
         <v>1</v>
+      </c>
+      <c r="II26">
+        <v>3</v>
+      </c>
+      <c r="IO26">
+        <v>3</v>
       </c>
       <c r="JD26">
         <v>1</v>
@@ -3488,8 +3506,14 @@
       <c r="CH31">
         <v>1</v>
       </c>
+      <c r="CM31">
+        <v>3</v>
+      </c>
       <c r="CR31">
         <v>2</v>
+      </c>
+      <c r="CW31">
+        <v>3</v>
       </c>
       <c r="DA31">
         <v>1</v>
@@ -3625,6 +3649,12 @@
       </c>
       <c r="GN31">
         <v>1</v>
+      </c>
+      <c r="GT31">
+        <v>3</v>
+      </c>
+      <c r="HA31">
+        <v>3</v>
       </c>
       <c r="HE31">
         <v>1</v>
